--- a/src/New-release/Figure6.xlsx
+++ b/src/New-release/Figure6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30105"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://officenationalstatistics.sharepoint.com/sites/msdfp/fp/FLOVERVIEW/Floverview + LCLI 2025 IndQ4 - 2026 WEQ1/Figures/Templates/Data Vis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://officenationalstatistics.sharepoint.com/sites/msdfp/fp/FLOVERVIEW/Floverview + LCLI 2026 IndQ1 - 2026 WEQ2/Figures &amp; Tables/Templates/Data Vis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{2AC8B2F9-24A0-43FA-BFAD-461E2C3727B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9D96C55-4D79-4A39-B29D-18170EE21FC4}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{2AC8B2F9-24A0-43FA-BFAD-461E2C3727B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{101C5087-28AE-49AB-9CF1-30645F680BAC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,12 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
-  <si>
-    <t>Figure 6: In 2025Q4 the information and communication industry made the biggest upward contribution to output per hour in comparison with the 2019 average </t>
-  </si>
-  <si>
-    <t>Contribution to growth of output per hour worked, percentage points, 2025Q4 compared with 2019 average</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+  <si>
+    <t>Figure 6: The information and communication industry has made the largest upward contribution to UK output per hour growth since 2019contribution to output per hour in comparison with the 2019 average</t>
+  </si>
+  <si>
+    <t>Contribution to growth of output per hour worked, percentage points, Quarter 1 (Jan to Mar) 2025 compared with 2019 average</t>
   </si>
   <si>
     <t>Notes</t>
@@ -67,13 +67,10 @@
     </r>
   </si>
   <si>
-    <t>2. "Other services" industry includes: activities of households as employers, undifferentiated goods and services producing activities of households for own use, activities of membership organisations, repair of computers and personal and household goods and a variety of personal service activities not covered elsewhere in our Standard Industrial Classification (SIC) 2007</t>
-  </si>
-  <si>
-    <t>3. The relative size of an industry shown is based on the Current Price (CP) value from 2019</t>
-  </si>
-  <si>
-    <t>4. Even if every industry were to experience zero productivity growth, the whole economy could still grow if higher productivity sectors expand while lower productivity sectors contract, this is known as a reallocation effect. A positive reallocation effect indicates that economic activity has shifted, on average, from lower‑productivity industries to higher‑productivity ones, while a negative reallocation effect indicates the reverse.</t>
+    <t>2. The "other services" industry includes activities of households as employers, undifferentiated goods and services producing activities of households for own use, activities of membership organisations, repair of computers and personal and household goods and a variety of personal service activities not covered elsewhere in our Standard Industrial Classification (SIC) 2007</t>
+  </si>
+  <si>
+    <t>3. The relative size of an industry shown is based on the current price (CP) value from 2019 (average).</t>
   </si>
   <si>
     <t>Unit</t>
@@ -97,22 +94,28 @@
     <t>Information and communication</t>
   </si>
   <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
     <t>Professional, scientific and technical activities</t>
   </si>
   <si>
-    <t>Manufacturing</t>
-  </si>
-  <si>
     <t>Administrative and support service activities</t>
   </si>
   <si>
     <t>Transport and storage</t>
   </si>
   <si>
+    <t>Agriculture, forestry and fishing</t>
+  </si>
+  <si>
     <t>Construction</t>
   </si>
   <si>
-    <t>Agriculture, forestry and fishing</t>
+    <t>Arts, entertainment and recreation</t>
+  </si>
+  <si>
+    <t>Wholesale and retail, trade; repair of motor vehicles and motor cycle</t>
   </si>
   <si>
     <t>Public administration and defence; compulsory social security</t>
@@ -121,25 +124,19 @@
     <t>Water supply; sewerage, waste management and remediation activities</t>
   </si>
   <si>
-    <t>Wholesale and retail, trade; repair of motor vehicles and motor cycle</t>
+    <t>Accommodation and food service activities</t>
   </si>
   <si>
     <t>Other service activities &amp; Activities of households as employers</t>
   </si>
   <si>
-    <t>Arts, entertainment and recreation</t>
-  </si>
-  <si>
-    <t>Accommodation and food service activities</t>
+    <t>Education</t>
   </si>
   <si>
     <t>Mining and quarrying</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>Real estate activities exluding imputed rental</t>
+    <t>Real estate activities excluding imputed rental</t>
   </si>
   <si>
     <t>Financial and insurance activities</t>
@@ -184,12 +181,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -204,10 +207,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -581,10 +585,8 @@
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" ht="15">
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
+    <row r="7" spans="1:3">
+      <c r="B7" s="3"/>
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3">
@@ -595,238 +597,238 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="15">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>9</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>10</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="15">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
       <c r="B13" s="2">
-        <v>2.0055584926665402E-2</v>
+        <v>2.9247907186752801E-2</v>
       </c>
       <c r="C13" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>2.4648964839277698E-2</v>
+        <v>2.7502367311605502E-2</v>
       </c>
       <c r="C14" s="2">
         <v>6.9091985072051998E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1.4955810100198299E-2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.11046921711254699</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
-        <v>1.2435734658281501E-2</v>
-      </c>
-      <c r="C15" s="2">
+      <c r="B16" s="2">
+        <v>1.42015677614359E-2</v>
+      </c>
+      <c r="C16" s="2">
         <v>8.6069359491453903E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15">
-      <c r="A16" t="s">
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
-        <v>1.17879625389478E-2</v>
-      </c>
-      <c r="C16" s="2">
-        <v>0.11046921711254699</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
       <c r="B17" s="2">
-        <v>6.1231617202346603E-3</v>
+        <v>5.7218609028187395E-3</v>
       </c>
       <c r="C17" s="2">
         <v>5.6393074969482399E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>4.7072065904719502E-3</v>
+        <v>3.2318614818730601E-3</v>
       </c>
       <c r="C18" s="2">
         <v>4.4110710518787601E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>1.34036662251202E-3</v>
+      </c>
+      <c r="C19" s="2">
+        <v>7.0960162294484101E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2">
-        <v>2.15988556118233E-3</v>
-      </c>
-      <c r="C19" s="2">
+      <c r="B20" s="2">
+        <v>4.5682251030335102E-4</v>
+      </c>
+      <c r="C20" s="2">
         <v>6.8666704517909793E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15">
-      <c r="A20" t="s">
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2">
-        <v>1.77141034052604E-3</v>
-      </c>
-      <c r="C20" s="2">
-        <v>7.0960162294484101E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15">
-      <c r="A21" t="s">
+      <c r="B21" s="2">
+        <v>3.2191937229083899E-4</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1.64363564102172E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2">
-        <v>3.3227090667189903E-4</v>
-      </c>
-      <c r="C21" s="2">
+      <c r="B22" s="2">
+        <v>-3.4848627471022295E-4</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.113281309711245</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>-3.6456923370398501E-4</v>
+      </c>
+      <c r="C23" s="2">
         <v>5.3101108677470199E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2">
-        <v>1.7179337748827499E-4</v>
-      </c>
-      <c r="C22" s="2">
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>-4.8127033767326403E-4</v>
+      </c>
+      <c r="C24" s="2">
         <v>1.33884214502994E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2">
-        <v>-7.3670533353602794E-4</v>
-      </c>
-      <c r="C23" s="2">
-        <v>0.113281309711245</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15">
-      <c r="A24" t="s">
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2">
-        <v>-1.03349608118808E-3</v>
-      </c>
-      <c r="C24" s="2">
+      <c r="B25" s="2">
+        <v>-1.0785638254560701E-3</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3.2992817726610599E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>-1.86968685046072E-3</v>
+      </c>
+      <c r="C26" s="2">
         <v>2.11908729006208E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2">
-        <v>-1.03545152643478E-3</v>
-      </c>
-      <c r="C25" s="2">
-        <v>1.64363564102172E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="15">
-      <c r="A26" t="s">
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="2">
-        <v>-1.1773322338788899E-3</v>
-      </c>
-      <c r="C26" s="2">
-        <v>3.2992817726610599E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="15">
-      <c r="A27" t="s">
+      <c r="B27" s="2">
+        <v>-2.1712752921432201E-3</v>
+      </c>
+      <c r="C27" s="2">
+        <v>6.3176272511480905E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="2">
-        <v>-2.57105282366494E-3</v>
-      </c>
-      <c r="C27" s="2">
+      <c r="B28" s="2">
+        <v>-3.1916396010944399E-3</v>
+      </c>
+      <c r="C28" s="2">
         <v>1.11561079895967E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15">
-      <c r="A28" t="s">
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="2">
-        <v>-4.1470420701393198E-3</v>
-      </c>
-      <c r="C28" s="2">
-        <v>6.3176272511480905E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="15">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
       <c r="B29" s="2">
-        <v>-5.1764672921483304E-3</v>
+        <v>-6.4878764501919194E-3</v>
       </c>
       <c r="C29" s="2">
         <v>4.3964400905809303E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>-7.8056216278159897E-3</v>
+        <v>-7.8612440001718693E-3</v>
       </c>
       <c r="C30" s="2">
         <v>8.9521283681237199E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>-8.5331617125305199E-3</v>
+        <v>-8.25926925717246E-3</v>
       </c>
       <c r="C31" s="2">
         <v>1.6158477331836701E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>-1.1259174182559699E-2</v>
+        <v>-8.9012511787603596E-3</v>
       </c>
       <c r="C32" s="2">
         <v>8.3735502791893096E-2</v>
@@ -834,10 +836,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>-6.0730072252020303E-4</v>
+        <v>2.53046342525356E-3</v>
       </c>
       <c r="C33" s="2"/>
     </row>
@@ -847,14 +849,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8a54c791-04d1-4dd7-97a3-a882d4048403">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1107,16 +1107,18 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8a54c791-04d1-4dd7-97a3-a882d4048403">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDAD2DC3-87EC-4167-B2AD-C5DBB7ECB4E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8557CAEA-ABFE-4BAB-A82C-A482A20DAFD5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1124,7 +1126,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8557CAEA-ABFE-4BAB-A82C-A482A20DAFD5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDAD2DC3-87EC-4167-B2AD-C5DBB7ECB4E8}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
